--- a/sample/ExcelMacro/kabuSTATION_API_function_sample.xlsx
+++ b/sample/ExcelMacro/kabuSTATION_API_function_sample.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\15.MSSOR_Ph2\kabusapi\sample\ExcelMacro\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816D03C6-A3BF-4FB5-A4EF-E1853DFF697C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F40A181-857F-4251-BF31-8B33B82773EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="787" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="787" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="注文取消" sheetId="1" r:id="rId1"/>
@@ -28,9 +23,10 @@
     <sheet name="優先市場" sheetId="17" r:id="rId13"/>
     <sheet name="ソフトリミット" sheetId="18" r:id="rId14"/>
     <sheet name="プレミアム料取得" sheetId="19" r:id="rId15"/>
-    <sheet name="銘柄登録" sheetId="7" r:id="rId16"/>
-    <sheet name="銘柄登録解除" sheetId="8" r:id="rId17"/>
-    <sheet name="銘柄登録全解除" sheetId="9" r:id="rId18"/>
+    <sheet name="歩み値取得" sheetId="21" r:id="rId16"/>
+    <sheet name="銘柄登録" sheetId="7" r:id="rId17"/>
+    <sheet name="銘柄登録解除" sheetId="8" r:id="rId18"/>
+    <sheet name="銘柄登録全解除" sheetId="9" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">注文約定照会!$B$5:$J$8</definedName>
@@ -56,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="588">
   <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
@@ -3208,6 +3204,79 @@
     <t>東証+</t>
     <rPh sb="0" eb="2">
       <t>トウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>歩み値情報を取得する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TIMEANDSALES</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出来時刻</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出来高</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出来値</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※歩み値のリクエストは秒間2件の流量制限を設けております。</t>
+    <rPh sb="1" eb="2">
+      <t>アユ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ビョウカン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>リュウリョウセイゲン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>=TIMEANDSALES(C8,D8)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>歩み値合計件数</t>
+    <rPh sb="0" eb="1">
+      <t>アユ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>銘柄あたり建玉上限額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>限週</t>
+    <rPh sb="0" eb="1">
+      <t>カギシュウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3719,7 +3788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -3918,7 +3987,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3993,6 +4061,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4639,22 +4709,22 @@
       <c r="C10" s="65" t="s">
         <v>348</v>
       </c>
-      <c r="D10" s="172" t="s">
+      <c r="D10" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="E10" s="173"/>
+      <c r="E10" s="174"/>
       <c r="H10" s="65" t="s">
         <v>348</v>
       </c>
-      <c r="I10" s="172" t="s">
+      <c r="I10" s="173" t="s">
         <v>264</v>
       </c>
-      <c r="J10" s="173"/>
-      <c r="K10" s="174" t="s">
+      <c r="J10" s="174"/>
+      <c r="K10" s="175" t="s">
         <v>296</v>
       </c>
-      <c r="L10" s="174"/>
-      <c r="M10" s="174"/>
+      <c r="L10" s="175"/>
+      <c r="M10" s="175"/>
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="80" t="s">
@@ -4670,18 +4740,18 @@
       <c r="G11" s="86" t="s">
         <v>312</v>
       </c>
-      <c r="H11" s="142" t="s">
+      <c r="H11" s="141" t="s">
         <v>310</v>
       </c>
       <c r="I11" s="82" t="s">
         <v>364</v>
       </c>
       <c r="J11" s="74"/>
-      <c r="K11" s="175" t="s">
+      <c r="K11" s="176" t="s">
         <v>544</v>
       </c>
-      <c r="L11" s="176"/>
-      <c r="M11" s="177"/>
+      <c r="L11" s="177"/>
+      <c r="M11" s="178"/>
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="83"/>
@@ -4693,16 +4763,16 @@
       </c>
       <c r="E12" s="74"/>
       <c r="G12" s="84"/>
-      <c r="H12" s="142" t="s">
+      <c r="H12" s="141" t="s">
         <v>365</v>
       </c>
       <c r="I12" s="82" t="s">
         <v>366</v>
       </c>
       <c r="J12" s="74"/>
-      <c r="K12" s="178"/>
-      <c r="L12" s="179"/>
-      <c r="M12" s="180"/>
+      <c r="K12" s="179"/>
+      <c r="L12" s="180"/>
+      <c r="M12" s="181"/>
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="83"/>
@@ -4714,17 +4784,17 @@
       </c>
       <c r="E13" s="74"/>
       <c r="G13" s="84"/>
-      <c r="H13" s="143" t="s">
+      <c r="H13" s="142" t="s">
         <v>538</v>
       </c>
-      <c r="I13" s="144" t="s">
+      <c r="I13" s="143" t="s">
         <v>541</v>
       </c>
       <c r="J13" s="74"/>
-      <c r="K13" s="178"/>
-      <c r="L13" s="179"/>
-      <c r="M13" s="180"/>
-      <c r="N13" s="141"/>
+      <c r="K13" s="179"/>
+      <c r="L13" s="180"/>
+      <c r="M13" s="181"/>
+      <c r="N13" s="140"/>
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="83"/>
@@ -4736,17 +4806,17 @@
       </c>
       <c r="E14" s="74"/>
       <c r="G14" s="84"/>
-      <c r="H14" s="143" t="s">
+      <c r="H14" s="142" t="s">
         <v>539</v>
       </c>
-      <c r="I14" s="144" t="s">
+      <c r="I14" s="143" t="s">
         <v>542</v>
       </c>
       <c r="J14" s="74"/>
-      <c r="K14" s="178"/>
-      <c r="L14" s="179"/>
-      <c r="M14" s="180"/>
-      <c r="N14" s="141"/>
+      <c r="K14" s="179"/>
+      <c r="L14" s="180"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="140"/>
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="83"/>
@@ -4758,17 +4828,17 @@
       </c>
       <c r="E15" s="74"/>
       <c r="G15" s="84"/>
-      <c r="H15" s="143" t="s">
+      <c r="H15" s="142" t="s">
         <v>540</v>
       </c>
-      <c r="I15" s="144" t="s">
+      <c r="I15" s="143" t="s">
         <v>543</v>
       </c>
       <c r="J15" s="74"/>
-      <c r="K15" s="178"/>
-      <c r="L15" s="179"/>
-      <c r="M15" s="180"/>
-      <c r="N15" s="141"/>
+      <c r="K15" s="179"/>
+      <c r="L15" s="180"/>
+      <c r="M15" s="181"/>
+      <c r="N15" s="140"/>
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="83"/>
@@ -4780,16 +4850,16 @@
       </c>
       <c r="E16" s="74"/>
       <c r="G16" s="84"/>
-      <c r="H16" s="142" t="s">
+      <c r="H16" s="141" t="s">
         <v>367</v>
       </c>
       <c r="I16" s="82" t="s">
         <v>368</v>
       </c>
       <c r="J16" s="74"/>
-      <c r="K16" s="178"/>
-      <c r="L16" s="179"/>
-      <c r="M16" s="180"/>
+      <c r="K16" s="179"/>
+      <c r="L16" s="180"/>
+      <c r="M16" s="181"/>
     </row>
     <row r="17" spans="2:18">
       <c r="B17" s="83"/>
@@ -4801,16 +4871,16 @@
       </c>
       <c r="E17" s="74"/>
       <c r="G17" s="84"/>
-      <c r="H17" s="142" t="s">
+      <c r="H17" s="141" t="s">
         <v>369</v>
       </c>
       <c r="I17" s="82" t="s">
         <v>194</v>
       </c>
       <c r="J17" s="74"/>
-      <c r="K17" s="178"/>
-      <c r="L17" s="179"/>
-      <c r="M17" s="180"/>
+      <c r="K17" s="179"/>
+      <c r="L17" s="180"/>
+      <c r="M17" s="181"/>
     </row>
     <row r="18" spans="2:18">
       <c r="B18" s="83"/>
@@ -4822,16 +4892,16 @@
       </c>
       <c r="E18" s="74"/>
       <c r="G18" s="85"/>
-      <c r="H18" s="142" t="s">
+      <c r="H18" s="141" t="s">
         <v>370</v>
       </c>
       <c r="I18" s="82" t="s">
         <v>371</v>
       </c>
       <c r="J18" s="74"/>
-      <c r="K18" s="181"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="183"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="183"/>
+      <c r="M18" s="184"/>
     </row>
     <row r="19" spans="2:18">
       <c r="B19" s="84"/>
@@ -7377,7 +7447,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="146" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="114" t="s">
@@ -7388,7 +7458,7 @@
       <c r="F2" s="116"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="147" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="114" t="s">
@@ -7404,17 +7474,17 @@
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="C6" s="119" t="s">
+      <c r="C6" s="118" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="C7" s="120" t="s">
+      <c r="C7" s="119" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="120" t="s">
         <v>291</v>
       </c>
     </row>
@@ -7429,64 +7499,64 @@
       <c r="C12" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="122" t="s">
+      <c r="D12" s="121" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="D13" s="123"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="126" t="s">
+      <c r="D13" s="122"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="125" t="s">
         <v>521</v>
       </c>
-      <c r="H13" s="125"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="125"/>
-      <c r="K13" s="125"/>
-      <c r="L13" s="125"/>
-      <c r="M13" s="126" t="s">
+      <c r="H13" s="124"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="125" t="s">
         <v>522</v>
       </c>
-      <c r="N13" s="127"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="122"/>
     </row>
     <row r="14" spans="2:16">
-      <c r="C14" s="119" t="s">
+      <c r="C14" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="128" t="s">
+      <c r="D14" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="137" t="s">
+      <c r="E14" s="136" t="s">
         <v>510</v>
       </c>
-      <c r="F14" s="137" t="s">
+      <c r="F14" s="136" t="s">
         <v>514</v>
       </c>
-      <c r="G14" s="137" t="s">
+      <c r="G14" s="136" t="s">
         <v>516</v>
       </c>
-      <c r="H14" s="137" t="s">
+      <c r="H14" s="136" t="s">
         <v>517</v>
       </c>
-      <c r="I14" s="137" t="s">
+      <c r="I14" s="136" t="s">
         <v>528</v>
       </c>
-      <c r="J14" s="137" t="s">
+      <c r="J14" s="136" t="s">
         <v>510</v>
       </c>
-      <c r="K14" s="137" t="s">
+      <c r="K14" s="136" t="s">
         <v>514</v>
       </c>
-      <c r="L14" s="137" t="s">
+      <c r="L14" s="136" t="s">
         <v>516</v>
       </c>
-      <c r="M14" s="137" t="s">
+      <c r="M14" s="136" t="s">
         <v>517</v>
       </c>
-      <c r="N14" s="137" t="s">
+      <c r="N14" s="136" t="s">
         <v>528</v>
       </c>
     </row>
@@ -7495,159 +7565,159 @@
         <f>"(D"&amp;ROW()&amp;"に関数入力)"</f>
         <v>(D15に関数入力)</v>
       </c>
-      <c r="D15" s="129" t="s">
+      <c r="D15" s="128" t="s">
         <v>519</v>
       </c>
-      <c r="E15" s="129" t="s">
+      <c r="E15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="129" t="s">
+      <c r="F15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="129" t="s">
+      <c r="G15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="129" t="s">
+      <c r="H15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="129" t="s">
+      <c r="I15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="129" t="s">
+      <c r="J15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="129" t="s">
+      <c r="K15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="129" t="s">
+      <c r="L15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="129" t="s">
+      <c r="M15" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="N15" s="129" t="s">
+      <c r="N15" s="128" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:16">
-      <c r="D16" s="129"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="129"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="128"/>
+      <c r="J16" s="128"/>
+      <c r="K16" s="128"/>
+      <c r="L16" s="128"/>
+      <c r="M16" s="128"/>
+      <c r="N16" s="128"/>
     </row>
     <row r="17" spans="3:14">
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="129"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="129"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="128"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="128"/>
     </row>
     <row r="18" spans="3:14">
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="129"/>
-      <c r="G18" s="129"/>
-      <c r="H18" s="129"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="129"/>
-      <c r="K18" s="129"/>
-      <c r="L18" s="129"/>
-      <c r="M18" s="129"/>
-      <c r="N18" s="129"/>
+      <c r="D18" s="128"/>
+      <c r="E18" s="128"/>
+      <c r="F18" s="128"/>
+      <c r="G18" s="128"/>
+      <c r="H18" s="128"/>
+      <c r="I18" s="128"/>
+      <c r="J18" s="128"/>
+      <c r="K18" s="128"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="128"/>
+      <c r="N18" s="128"/>
     </row>
     <row r="19" spans="3:14">
-      <c r="D19" s="129"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="129"/>
-      <c r="G19" s="129"/>
-      <c r="H19" s="129"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="129"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="129"/>
-      <c r="M19" s="129"/>
-      <c r="N19" s="129"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
     </row>
     <row r="20" spans="3:14">
-      <c r="D20" s="129"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="129"/>
-      <c r="G20" s="129"/>
-      <c r="H20" s="129"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="129"/>
-      <c r="K20" s="129"/>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="129"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
     </row>
     <row r="23" spans="3:14">
-      <c r="C23" s="130" t="s">
+      <c r="C23" s="129" t="s">
         <v>510</v>
       </c>
-      <c r="D23" s="131" t="s">
+      <c r="D23" s="130" t="s">
         <v>511</v>
       </c>
-      <c r="E23" s="184" t="s">
+      <c r="E23" s="185" t="s">
         <v>512</v>
       </c>
-      <c r="F23" s="185"/>
+      <c r="F23" s="186"/>
     </row>
     <row r="24" spans="3:14">
-      <c r="C24" s="140"/>
-      <c r="D24" s="133" t="s">
+      <c r="C24" s="139"/>
+      <c r="D24" s="132" t="s">
         <v>533</v>
       </c>
-      <c r="E24" s="186" t="s">
+      <c r="E24" s="187" t="s">
         <v>534</v>
       </c>
-      <c r="F24" s="186"/>
+      <c r="F24" s="187"/>
     </row>
     <row r="25" spans="3:14">
-      <c r="C25" s="132"/>
-      <c r="D25" s="133">
+      <c r="C25" s="131"/>
+      <c r="D25" s="132">
         <v>0</v>
       </c>
-      <c r="E25" s="187" t="s">
+      <c r="E25" s="188" t="s">
         <v>535</v>
       </c>
-      <c r="F25" s="187"/>
+      <c r="F25" s="188"/>
     </row>
     <row r="26" spans="3:14">
-      <c r="C26" s="132"/>
-      <c r="D26" s="134">
+      <c r="C26" s="131"/>
+      <c r="D26" s="133">
         <v>1</v>
       </c>
-      <c r="E26" s="188" t="s">
+      <c r="E26" s="189" t="s">
         <v>536</v>
       </c>
-      <c r="F26" s="188"/>
+      <c r="F26" s="189"/>
     </row>
     <row r="27" spans="3:14">
-      <c r="C27" s="135"/>
-      <c r="D27" s="133">
+      <c r="C27" s="134"/>
+      <c r="D27" s="132">
         <v>2</v>
       </c>
-      <c r="E27" s="187" t="s">
+      <c r="E27" s="188" t="s">
         <v>537</v>
       </c>
-      <c r="F27" s="187"/>
+      <c r="F27" s="188"/>
     </row>
     <row r="29" spans="3:14">
-      <c r="D29" s="138" t="s">
+      <c r="D29" s="137" t="s">
         <v>527</v>
       </c>
       <c r="E29" s="117" t="s">
@@ -7655,7 +7725,7 @@
       </c>
     </row>
     <row r="30" spans="3:14">
-      <c r="D30" s="139"/>
+      <c r="D30" s="138"/>
       <c r="E30" s="117" t="s">
         <v>524</v>
       </c>
@@ -7671,7 +7741,7 @@
       </c>
     </row>
     <row r="33" spans="4:5">
-      <c r="D33" s="139" t="s">
+      <c r="D33" s="138" t="s">
         <v>532</v>
       </c>
       <c r="E33" s="117" t="s">
@@ -7679,7 +7749,7 @@
       </c>
     </row>
     <row r="34" spans="4:5">
-      <c r="D34" s="139" t="s">
+      <c r="D34" s="138" t="s">
         <v>530</v>
       </c>
       <c r="E34" s="117" t="s">
@@ -7687,7 +7757,7 @@
       </c>
     </row>
     <row r="40" spans="4:5">
-      <c r="D40" s="136"/>
+      <c r="D40" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7704,6 +7774,279 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9CBCEE-3B31-4688-94AB-19F8F6D98371}">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="3" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="18.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="117"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="117"/>
+      <c r="B2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="114" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="116"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="117"/>
+      <c r="B3" s="147" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="114" t="s">
+        <v>579</v>
+      </c>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="116"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="6"/>
+      <c r="C7" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="C10" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="C11" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="23">
+        <v>1</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="C12" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="23">
+        <v>3</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="C13" s="33"/>
+      <c r="D13" s="23">
+        <v>5</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="C14" s="34"/>
+      <c r="D14" s="23">
+        <v>6</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="C15" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="C16" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="D16" s="23">
+        <v>23</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="C17" s="34"/>
+      <c r="D17" s="23">
+        <v>24</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="C21" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="C22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="C23" s="27" t="str">
+        <f>"(D"&amp;ROW()&amp;"に関数入力)"</f>
+        <v>(D23に関数入力)</v>
+      </c>
+      <c r="D23" s="7">
+        <v>8306</v>
+      </c>
+      <c r="E23" s="23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="23">
+        <v>5</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="G24" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="G25" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="G26" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="G27" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>583</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{6A91A987-CD97-45A9-807C-CA71CE2664E6}">
+      <formula1>"1,3,5,6,2,23,24"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A2:H40"/>
@@ -8068,10 +8411,11 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A2:H40"/>
@@ -8397,10 +8741,11 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A2:H20"/>
@@ -8712,12 +9057,12 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="H20" s="145" t="s">
+      <c r="H20" s="144" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="H21" s="145" t="s">
+      <c r="H21" s="144" t="s">
         <v>550</v>
       </c>
     </row>
@@ -8736,7 +9081,7 @@
       <c r="D23" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="H23" s="146" t="s">
+      <c r="H23" s="145" t="s">
         <v>551</v>
       </c>
     </row>
@@ -10653,12 +10998,13 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:AA28"/>
+  <dimension ref="A2:AC28"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -10674,13 +11020,15 @@
     <col min="12" max="13" width="8.375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.25" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.25" customWidth="1"/>
+    <col min="25" max="26" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8">
@@ -10834,7 +11182,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:29">
       <c r="C17" s="34"/>
       <c r="D17" s="23">
         <v>24</v>
@@ -10843,15 +11191,15 @@
         <v>259</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:29">
       <c r="B19" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:29">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:29">
       <c r="B21" s="5"/>
       <c r="C21" t="s">
         <v>196</v>
@@ -10860,7 +11208,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:29">
       <c r="C22" s="6" t="s">
         <v>10</v>
       </c>
@@ -10910,34 +11258,40 @@
         <v>97</v>
       </c>
       <c r="S22" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="T22" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="T22" s="8" t="s">
+      <c r="U22" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="V22" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="V22" s="8" t="s">
+      <c r="W22" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="W22" s="8" t="s">
+      <c r="X22" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="Y22" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="X22" s="8" t="s">
+      <c r="Z22" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="Y22" s="8" t="s">
+      <c r="AA22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="Z22" s="8" t="s">
+      <c r="AB22" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="AA22" s="8" t="s">
+      <c r="AC22" s="8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:29">
       <c r="A23" s="6"/>
       <c r="C23" s="27" t="str">
         <f>"(D"&amp;ROW()&amp;"に関数入力)"</f>
@@ -11015,8 +11369,14 @@
       <c r="AA23" s="7" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AB23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC23" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -11042,23 +11402,25 @@
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+    </row>
+    <row r="25" spans="1:29">
       <c r="B25" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:29">
       <c r="B26" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:29">
       <c r="B27" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:29">
       <c r="B28" s="89" t="s">
         <v>307</v>
       </c>
@@ -11074,6 +11436,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11229,89 +11592,89 @@
       <c r="C11" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="D11" s="155" t="s">
+      <c r="D11" s="156" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="156"/>
-      <c r="F11" s="155" t="s">
+      <c r="E11" s="157"/>
+      <c r="F11" s="156" t="s">
         <v>296</v>
       </c>
-      <c r="G11" s="156"/>
+      <c r="G11" s="157"/>
       <c r="L11" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="172" t="s">
         <v>275</v>
       </c>
       <c r="C12" s="42">
         <v>0</v>
       </c>
-      <c r="D12" s="167" t="s">
+      <c r="D12" s="168" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="168"/>
-      <c r="F12" s="157" t="s">
+      <c r="E12" s="169"/>
+      <c r="F12" s="158" t="s">
         <v>297</v>
       </c>
-      <c r="G12" s="158"/>
+      <c r="G12" s="159"/>
       <c r="L12" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="171"/>
+      <c r="B13" s="172"/>
       <c r="C13" s="42">
         <v>1</v>
       </c>
-      <c r="D13" s="167" t="s">
+      <c r="D13" s="168" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="168"/>
-      <c r="F13" s="159" t="s">
+      <c r="E13" s="169"/>
+      <c r="F13" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="G13" s="160"/>
+      <c r="G13" s="161"/>
       <c r="L13" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="171"/>
+      <c r="B14" s="172"/>
       <c r="C14" s="42">
         <v>2</v>
       </c>
-      <c r="D14" s="167" t="s">
+      <c r="D14" s="168" t="s">
         <v>199</v>
       </c>
-      <c r="E14" s="168"/>
-      <c r="F14" s="159"/>
-      <c r="G14" s="160"/>
+      <c r="E14" s="169"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="161"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="171"/>
+      <c r="B15" s="172"/>
       <c r="C15" s="42">
         <v>3</v>
       </c>
-      <c r="D15" s="167" t="s">
+      <c r="D15" s="168" t="s">
         <v>262</v>
       </c>
-      <c r="E15" s="168"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="160"/>
+      <c r="E15" s="169"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="161"/>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="171"/>
+      <c r="B16" s="172"/>
       <c r="C16" s="42">
         <v>4</v>
       </c>
-      <c r="D16" s="167" t="s">
+      <c r="D16" s="168" t="s">
         <v>263</v>
       </c>
-      <c r="E16" s="168"/>
-      <c r="F16" s="161"/>
-      <c r="G16" s="162"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="163"/>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="58" t="s">
@@ -11366,30 +11729,30 @@
       <c r="G20" s="62"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="169" t="s">
+      <c r="B21" s="170" t="s">
         <v>284</v>
       </c>
       <c r="C21" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="167" t="s">
+      <c r="D21" s="168" t="s">
         <v>302</v>
       </c>
-      <c r="E21" s="168"/>
+      <c r="E21" s="169"/>
       <c r="F21" s="66" t="s">
         <v>297</v>
       </c>
       <c r="G21" s="67"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="169"/>
+      <c r="B22" s="170"/>
       <c r="C22" s="42" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="167" t="s">
+      <c r="D22" s="168" t="s">
         <v>303</v>
       </c>
-      <c r="E22" s="168"/>
+      <c r="E22" s="169"/>
       <c r="F22" s="68" t="s">
         <v>305</v>
       </c>
@@ -11412,130 +11775,130 @@
       <c r="G23" s="64"/>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="169" t="s">
+      <c r="B24" s="170" t="s">
         <v>287</v>
       </c>
       <c r="C24" s="41">
         <v>1</v>
       </c>
-      <c r="D24" s="165" t="s">
+      <c r="D24" s="166" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="166"/>
-      <c r="F24" s="163" t="s">
+      <c r="E24" s="167"/>
+      <c r="F24" s="164" t="s">
         <v>297</v>
       </c>
-      <c r="G24" s="164"/>
+      <c r="G24" s="165"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="169"/>
+      <c r="B25" s="170"/>
       <c r="C25" s="41">
         <v>2</v>
       </c>
-      <c r="D25" s="153" t="s">
+      <c r="D25" s="154" t="s">
         <v>276</v>
       </c>
-      <c r="E25" s="154"/>
-      <c r="F25" s="147" t="s">
+      <c r="E25" s="155"/>
+      <c r="F25" s="148" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="148"/>
+      <c r="G25" s="149"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="169"/>
+      <c r="B26" s="170"/>
       <c r="C26" s="41">
         <v>3</v>
       </c>
-      <c r="D26" s="153" t="s">
+      <c r="D26" s="154" t="s">
         <v>277</v>
       </c>
-      <c r="E26" s="154"/>
-      <c r="F26" s="147"/>
-      <c r="G26" s="148"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="149"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="169"/>
+      <c r="B27" s="170"/>
       <c r="C27" s="41">
         <v>4</v>
       </c>
-      <c r="D27" s="153" t="s">
+      <c r="D27" s="154" t="s">
         <v>278</v>
       </c>
-      <c r="E27" s="154"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="148"/>
+      <c r="E27" s="155"/>
+      <c r="F27" s="148"/>
+      <c r="G27" s="149"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="169"/>
+      <c r="B28" s="170"/>
       <c r="C28" s="41">
         <v>5</v>
       </c>
-      <c r="D28" s="153" t="s">
+      <c r="D28" s="154" t="s">
         <v>279</v>
       </c>
-      <c r="E28" s="154"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="152"/>
+      <c r="E28" s="155"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="153"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="169" t="s">
+      <c r="B29" s="170" t="s">
         <v>288</v>
       </c>
       <c r="C29" s="41">
         <v>1</v>
       </c>
-      <c r="D29" s="165" t="s">
+      <c r="D29" s="166" t="s">
         <v>286</v>
       </c>
-      <c r="E29" s="166"/>
-      <c r="F29" s="163" t="s">
+      <c r="E29" s="167"/>
+      <c r="F29" s="164" t="s">
         <v>297</v>
       </c>
-      <c r="G29" s="164"/>
+      <c r="G29" s="165"/>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="169"/>
+      <c r="B30" s="170"/>
       <c r="C30" s="41">
         <v>2</v>
       </c>
-      <c r="D30" s="153" t="s">
+      <c r="D30" s="154" t="s">
         <v>280</v>
       </c>
-      <c r="E30" s="154"/>
-      <c r="F30" s="147" t="s">
+      <c r="E30" s="155"/>
+      <c r="F30" s="148" t="s">
         <v>304</v>
       </c>
-      <c r="G30" s="148"/>
+      <c r="G30" s="149"/>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="170" t="s">
+      <c r="B31" s="171" t="s">
         <v>289</v>
       </c>
       <c r="C31" s="41">
         <v>2</v>
       </c>
-      <c r="D31" s="153" t="s">
+      <c r="D31" s="154" t="s">
         <v>281</v>
       </c>
-      <c r="E31" s="154"/>
-      <c r="F31" s="149" t="s">
+      <c r="E31" s="155"/>
+      <c r="F31" s="150" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="150"/>
+      <c r="G31" s="151"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="170"/>
+      <c r="B32" s="171"/>
       <c r="C32" s="41">
         <v>3</v>
       </c>
-      <c r="D32" s="153" t="s">
+      <c r="D32" s="154" t="s">
         <v>282</v>
       </c>
-      <c r="E32" s="154"/>
-      <c r="F32" s="151" t="s">
+      <c r="E32" s="155"/>
+      <c r="F32" s="152" t="s">
         <v>304</v>
       </c>
-      <c r="G32" s="152"/>
+      <c r="G32" s="153"/>
     </row>
     <row r="33" spans="1:37">
       <c r="B33" s="6"/>
@@ -22984,6 +23347,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23203,6 +23567,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23386,6 +23751,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23545,5 +23911,6 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/sample/ExcelMacro/kabuSTATION_API_function_sample.xlsx
+++ b/sample/ExcelMacro/kabuSTATION_API_function_sample.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F40A181-857F-4251-BF31-8B33B82773EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C72B6F0-3FC4-4E82-A03E-FDD6F818879C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="787" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="787" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="注文取消" sheetId="1" r:id="rId1"/>
@@ -1854,13 +1854,7 @@
     <t>売残（千株）</t>
   </si>
   <si>
-    <t>売残前週比</t>
-  </si>
-  <si>
     <t>買残（千株）</t>
-  </si>
-  <si>
-    <t>買残前週比</t>
   </si>
   <si>
     <t>倍率</t>
@@ -3277,6 +3271,20 @@
     <t>限週</t>
     <rPh sb="0" eb="1">
       <t>カギシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>売残前日比</t>
+    <rPh sb="3" eb="4">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>買残前日比</t>
+    <rPh sb="3" eb="4">
+      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4063,16 +4071,37 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4081,17 +4110,23 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4105,38 +4140,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4471,22 +4479,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B2:I19"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="19.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4526,7 +4534,7 @@
     <row r="6" spans="2:9">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F6" s="26" t="s">
         <v>213</v>
@@ -4567,7 +4575,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -4600,7 +4608,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" spans="3:4">
@@ -4630,27 +4638,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B2:T64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.875" style="43" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" style="43" customWidth="1"/>
     <col min="2" max="2" width="14.25" style="43" customWidth="1"/>
     <col min="3" max="3" width="17" style="43" customWidth="1"/>
-    <col min="4" max="4" width="12.375" style="43" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="43" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="43" customWidth="1"/>
     <col min="7" max="7" width="12" style="43" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="43" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="43" customWidth="1"/>
-    <col min="10" max="10" width="14.625" style="43" customWidth="1"/>
+    <col min="8" max="8" width="12.58203125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="43" customWidth="1"/>
+    <col min="10" max="10" width="14.58203125" style="43" customWidth="1"/>
     <col min="11" max="11" width="19.75" style="43" customWidth="1"/>
-    <col min="12" max="12" width="16.875" style="43" customWidth="1"/>
-    <col min="13" max="13" width="20.625" style="43" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" style="43" customWidth="1"/>
+    <col min="13" max="13" width="20.58203125" style="43" customWidth="1"/>
     <col min="14" max="14" width="14.75" style="43" customWidth="1"/>
-    <col min="15" max="15" width="10.375" style="43" customWidth="1"/>
-    <col min="16" max="16" width="13.875" style="43" customWidth="1"/>
-    <col min="17" max="17" width="10.375" style="43" customWidth="1"/>
-    <col min="18" max="18" width="12.625" style="43" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="10.375" style="43" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="43" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" style="43" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" style="43" customWidth="1"/>
+    <col min="18" max="18" width="12.58203125" style="43" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="10.33203125" style="43" customWidth="1"/>
     <col min="25" max="16384" width="9" style="43"/>
   </cols>
   <sheetData>
@@ -4659,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D2" s="73"/>
       <c r="E2" s="73"/>
@@ -4670,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D3" s="73"/>
       <c r="E3" s="73"/>
@@ -4684,7 +4692,7 @@
     <row r="6" spans="2:14">
       <c r="B6" s="44"/>
       <c r="C6" s="44" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -4707,14 +4715,14 @@
     </row>
     <row r="10" spans="2:14">
       <c r="C10" s="65" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D10" s="173" t="s">
         <v>264</v>
       </c>
       <c r="E10" s="174"/>
       <c r="H10" s="65" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I10" s="173" t="s">
         <v>264</v>
@@ -4734,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="82" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E11" s="74"/>
       <c r="G11" s="86" t="s">
@@ -4744,11 +4752,11 @@
         <v>310</v>
       </c>
       <c r="I11" s="82" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J11" s="74"/>
       <c r="K11" s="176" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L11" s="177"/>
       <c r="M11" s="178"/>
@@ -4759,15 +4767,15 @@
         <v>2</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E12" s="74"/>
       <c r="G12" s="84"/>
       <c r="H12" s="141" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I12" s="82" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J12" s="74"/>
       <c r="K12" s="179"/>
@@ -4780,15 +4788,15 @@
         <v>3</v>
       </c>
       <c r="D13" s="82" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E13" s="74"/>
       <c r="G13" s="84"/>
       <c r="H13" s="142" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="I13" s="143" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J13" s="74"/>
       <c r="K13" s="179"/>
@@ -4802,15 +4810,15 @@
         <v>4</v>
       </c>
       <c r="D14" s="82" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E14" s="74"/>
       <c r="G14" s="84"/>
       <c r="H14" s="142" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I14" s="143" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J14" s="74"/>
       <c r="K14" s="179"/>
@@ -4824,15 +4832,15 @@
         <v>5</v>
       </c>
       <c r="D15" s="82" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E15" s="74"/>
       <c r="G15" s="84"/>
       <c r="H15" s="142" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I15" s="143" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J15" s="74"/>
       <c r="K15" s="179"/>
@@ -4846,15 +4854,15 @@
         <v>6</v>
       </c>
       <c r="D16" s="82" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E16" s="74"/>
       <c r="G16" s="84"/>
       <c r="H16" s="141" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="I16" s="82" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J16" s="74"/>
       <c r="K16" s="179"/>
@@ -4867,12 +4875,12 @@
         <v>7</v>
       </c>
       <c r="D17" s="82" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E17" s="74"/>
       <c r="G17" s="84"/>
       <c r="H17" s="141" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I17" s="82" t="s">
         <v>194</v>
@@ -4888,15 +4896,15 @@
         <v>8</v>
       </c>
       <c r="D18" s="82" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E18" s="74"/>
       <c r="G18" s="85"/>
       <c r="H18" s="141" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I18" s="82" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J18" s="74"/>
       <c r="K18" s="182"/>
@@ -4909,7 +4917,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="82" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E19" s="74"/>
       <c r="G19" s="78"/>
@@ -4920,7 +4928,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E20" s="74"/>
     </row>
@@ -4930,7 +4938,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="82" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E21" s="74"/>
     </row>
@@ -4940,7 +4948,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="82" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E22" s="74"/>
     </row>
@@ -4950,7 +4958,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="82" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E23" s="74"/>
     </row>
@@ -4960,7 +4968,7 @@
         <v>14</v>
       </c>
       <c r="D24" s="82" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E24" s="74"/>
     </row>
@@ -4970,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E25" s="74"/>
     </row>
@@ -4987,7 +4995,7 @@
         <v>196</v>
       </c>
       <c r="D30" s="79" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -5809,16 +5817,16 @@
         <v>340</v>
       </c>
       <c r="J55" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="K55" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="K55" s="8" t="s">
+      <c r="L55" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="M55" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="L55" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>344</v>
       </c>
       <c r="N55" s="8" t="s">
         <v>146</v>
@@ -5938,7 +5946,7 @@
         <v>196</v>
       </c>
       <c r="D60" s="79" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E60" s="78"/>
     </row>
@@ -5962,7 +5970,7 @@
         <v>315</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>334</v>
@@ -5974,7 +5982,7 @@
         <v>48</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N61" s="8" t="s">
         <v>333</v>
@@ -6101,22 +6109,22 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B2:I35"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="19.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="11" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6125,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6136,7 +6144,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D3" s="93"/>
       <c r="E3" s="93"/>
@@ -6150,21 +6158,21 @@
     <row r="6" spans="2:9">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F6" s="26"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="6"/>
       <c r="C7" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E7" s="24"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E8" s="25"/>
     </row>
@@ -6185,7 +6193,7 @@
         <v>196</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="2:9">
@@ -6193,16 +6201,16 @@
         <v>10</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>393</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>319</v>
@@ -6217,7 +6225,7 @@
         <v>(D14に関数入力)</v>
       </c>
       <c r="D14" s="95" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
@@ -6232,7 +6240,7 @@
         <v>12</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -6262,98 +6270,98 @@
     <row r="20" spans="2:9">
       <c r="B20" s="96"/>
       <c r="C20" s="97" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="C21" s="98" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D21" s="98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="C22" s="98" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D22" s="98" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="2:9">
       <c r="C23" s="98" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D23" s="98" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="2:9">
       <c r="C24" s="98" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D24" s="98" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="2:9">
       <c r="C25" s="98" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D25" s="98" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26" spans="2:9">
       <c r="C26" s="98" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D26" s="98" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="C27" s="98" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D27" s="98" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="2:9">
       <c r="C28" s="98" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D28" s="98" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="2:9">
       <c r="C29" s="98" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D29" s="98" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="2:9">
       <c r="C30" s="98" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D30" s="98" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="2:9">
       <c r="C31" s="98" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D31" s="98" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="2:2">
@@ -6386,26 +6394,26 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B2:N58"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="19.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="6" max="6" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.58203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.08203125" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="7.75" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -6413,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -6424,7 +6432,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D3" s="93"/>
       <c r="E3" s="93"/>
@@ -6438,7 +6446,7 @@
     <row r="6" spans="2:9">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F6" s="26"/>
     </row>
@@ -6448,7 +6456,7 @@
         <v>316</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E7" s="24"/>
     </row>
@@ -6465,159 +6473,159 @@
     <row r="10" spans="2:9">
       <c r="C10" s="100"/>
       <c r="D10" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E10" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G10" s="100"/>
       <c r="H10" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I10" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="C11" s="109" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D11" s="103" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E11" s="103" t="s">
+        <v>457</v>
+      </c>
+      <c r="G11" s="109" t="s">
+        <v>462</v>
+      </c>
+      <c r="H11" s="103" t="s">
         <v>459</v>
       </c>
-      <c r="G11" s="109" t="s">
-        <v>464</v>
-      </c>
-      <c r="H11" s="103" t="s">
+      <c r="I11" s="103" t="s">
         <v>461</v>
-      </c>
-      <c r="I11" s="103" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="12" spans="2:9">
       <c r="C12" s="106"/>
       <c r="D12" s="103" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E12" s="103" t="s">
+        <v>451</v>
+      </c>
+      <c r="G12" s="106" t="s">
+        <v>455</v>
+      </c>
+      <c r="H12" s="103" t="s">
         <v>453</v>
       </c>
-      <c r="G12" s="106" t="s">
-        <v>457</v>
-      </c>
-      <c r="H12" s="103" t="s">
-        <v>455</v>
-      </c>
       <c r="I12" s="103" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" spans="2:9">
       <c r="C13" s="106"/>
       <c r="D13" s="103" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E13" s="103" t="s">
+        <v>444</v>
+      </c>
+      <c r="G13" s="104" t="s">
+        <v>448</v>
+      </c>
+      <c r="H13" s="103" t="s">
         <v>446</v>
       </c>
-      <c r="G13" s="104" t="s">
-        <v>450</v>
-      </c>
-      <c r="H13" s="103" t="s">
-        <v>448</v>
-      </c>
       <c r="I13" s="103" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="2:9">
       <c r="C14" s="107"/>
       <c r="D14" s="103" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E14" s="102" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="3:14">
       <c r="C17" s="100"/>
       <c r="D17" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E17" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G17" s="100"/>
       <c r="H17" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I17" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" spans="3:14">
       <c r="C18" s="109" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D18" s="103" t="s">
+        <v>459</v>
+      </c>
+      <c r="E18" s="103" t="s">
         <v>461</v>
       </c>
-      <c r="E18" s="103" t="s">
-        <v>463</v>
-      </c>
       <c r="G18" s="109" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H18" s="103" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I18" s="103" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="3:14">
       <c r="C19" s="106"/>
       <c r="D19" s="103" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E19" s="103" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G19" s="106"/>
       <c r="H19" s="103" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I19" s="103" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="20" spans="3:14">
       <c r="C20" s="106"/>
       <c r="D20" s="103" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E20" s="103" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G20" s="104"/>
       <c r="H20" s="103" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I20" s="103" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="3:14">
       <c r="C21" s="106"/>
       <c r="D21" s="103" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E21" s="103" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L21" s="100"/>
       <c r="M21" s="101"/>
@@ -6626,10 +6634,10 @@
     <row r="22" spans="3:14">
       <c r="C22" s="106"/>
       <c r="D22" s="103" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E22" s="102" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="L22" s="100"/>
       <c r="M22" s="101"/>
@@ -6638,10 +6646,10 @@
     <row r="23" spans="3:14">
       <c r="C23" s="106"/>
       <c r="D23" s="103" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E23" s="103" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="L23" s="100"/>
       <c r="M23" s="101"/>
@@ -6650,10 +6658,10 @@
     <row r="24" spans="3:14">
       <c r="C24" s="106"/>
       <c r="D24" s="103" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E24" s="103" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="L24" s="100"/>
       <c r="M24" s="101"/>
@@ -6662,10 +6670,10 @@
     <row r="25" spans="3:14">
       <c r="C25" s="104"/>
       <c r="D25" s="103" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E25" s="103" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="L25" s="100"/>
       <c r="M25" s="101"/>
@@ -6684,10 +6692,10 @@
     <row r="28" spans="3:14">
       <c r="C28" s="100"/>
       <c r="D28" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E28" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L28" s="100"/>
       <c r="M28" s="101"/>
@@ -6695,13 +6703,13 @@
     </row>
     <row r="29" spans="3:14">
       <c r="C29" s="109" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D29" s="103" t="s">
+        <v>459</v>
+      </c>
+      <c r="E29" s="103" t="s">
         <v>461</v>
-      </c>
-      <c r="E29" s="103" t="s">
-        <v>463</v>
       </c>
       <c r="L29" s="100"/>
       <c r="M29" s="101"/>
@@ -6709,13 +6717,13 @@
     </row>
     <row r="30" spans="3:14">
       <c r="C30" s="108" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D30" s="103" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E30" s="103" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="L30" s="100"/>
       <c r="M30" s="101"/>
@@ -6723,13 +6731,13 @@
     </row>
     <row r="31" spans="3:14">
       <c r="C31" s="106" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D31" s="103" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E31" s="103" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="L31" s="100"/>
       <c r="M31" s="101"/>
@@ -6738,10 +6746,10 @@
     <row r="32" spans="3:14">
       <c r="C32" s="106"/>
       <c r="D32" s="103" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E32" s="103" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="L32" s="100"/>
       <c r="M32" s="101"/>
@@ -6750,10 +6758,10 @@
     <row r="33" spans="2:14">
       <c r="C33" s="106"/>
       <c r="D33" s="103" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E33" s="103" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L33" s="100"/>
       <c r="M33" s="101"/>
@@ -6762,10 +6770,10 @@
     <row r="34" spans="2:14">
       <c r="C34" s="106"/>
       <c r="D34" s="103" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E34" s="102" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L34" s="100"/>
       <c r="M34" s="101"/>
@@ -6774,10 +6782,10 @@
     <row r="35" spans="2:14">
       <c r="C35" s="106"/>
       <c r="D35" s="103" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E35" s="103" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L35" s="100"/>
       <c r="M35" s="101"/>
@@ -6786,10 +6794,10 @@
     <row r="36" spans="2:14">
       <c r="C36" s="106"/>
       <c r="D36" s="103" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E36" s="103" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L36" s="100"/>
       <c r="M36" s="101"/>
@@ -6798,10 +6806,10 @@
     <row r="37" spans="2:14">
       <c r="C37" s="105"/>
       <c r="D37" s="103" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E37" s="103" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L37" s="100"/>
       <c r="M37" s="101"/>
@@ -6810,10 +6818,10 @@
     <row r="38" spans="2:14">
       <c r="C38" s="104"/>
       <c r="D38" s="103" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E38" s="102" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L38" s="100"/>
       <c r="M38" s="101"/>
@@ -6843,7 +6851,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="2:14">
@@ -6854,25 +6862,25 @@
         <v>316</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H45" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="I45" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="I45" s="8" t="s">
-        <v>515</v>
-      </c>
       <c r="J45" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="46" spans="2:14">
@@ -6896,10 +6904,10 @@
         <v>12</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J46" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K46" s="23" t="s">
         <v>12</v>
@@ -6922,10 +6930,10 @@
         <v>12</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J47" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K47" s="23" t="s">
         <v>12</v>
@@ -6948,10 +6956,10 @@
         <v>12</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J48" s="23" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K48" s="23" t="s">
         <v>12</v>
@@ -7000,17 +7008,17 @@
     </row>
     <row r="56" spans="2:11">
       <c r="B56" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="B57" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -7028,23 +7036,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B2:F29"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="19.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7053,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D2" s="4"/>
     </row>
@@ -7062,7 +7070,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D3" s="94"/>
     </row>
@@ -7074,7 +7082,7 @@
     <row r="6" spans="2:6">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F6" s="26"/>
     </row>
@@ -7107,7 +7115,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" spans="2:6">
@@ -7118,7 +7126,7 @@
         <v>316</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="2:6">
@@ -7151,7 +7159,7 @@
     </row>
     <row r="19" spans="2:5">
       <c r="D19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -7160,48 +7168,48 @@
     <row r="21" spans="2:5">
       <c r="C21" s="100"/>
       <c r="D21" s="111" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E21" s="111" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="C22" s="109" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D22" s="103" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E22" s="103" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="C23" s="106"/>
       <c r="D23" s="103" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E23" s="103" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="C24" s="106"/>
       <c r="D24" s="103" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E24" s="103" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" s="107"/>
       <c r="D25" s="103" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E25" s="102" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -7232,23 +7240,23 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B2:K21"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="19.625" customWidth="1"/>
-    <col min="4" max="5" width="36.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.625" customWidth="1"/>
-    <col min="9" max="10" width="40.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="33.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.58203125" customWidth="1"/>
+    <col min="4" max="5" width="36.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.58203125" customWidth="1"/>
+    <col min="9" max="10" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7257,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
@@ -7267,7 +7275,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="92" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D3" s="93"/>
       <c r="E3" s="94"/>
@@ -7280,7 +7288,7 @@
     <row r="6" spans="2:11">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F6" s="26"/>
     </row>
@@ -7302,7 +7310,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:11">
@@ -7310,28 +7318,28 @@
         <v>10</v>
       </c>
       <c r="D11" s="91" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E11" s="91" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F11" s="91" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G11" s="91" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H11" s="91" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I11" s="91" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J11" s="91" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="2:11">
@@ -7436,10 +7444,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="B2:P40"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="9" style="117"/>
-    <col min="3" max="3" width="19.125" style="117" customWidth="1"/>
+    <col min="3" max="3" width="19.08203125" style="117" customWidth="1"/>
     <col min="4" max="4" width="18" style="117" customWidth="1"/>
     <col min="5" max="14" width="21" style="117" customWidth="1"/>
     <col min="15" max="16" width="22.25" style="117" bestFit="1" customWidth="1"/>
@@ -7451,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="114" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D2" s="115"/>
       <c r="E2" s="115"/>
@@ -7462,7 +7470,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="114" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D3" s="115"/>
       <c r="E3" s="115"/>
@@ -7475,7 +7483,7 @@
     </row>
     <row r="6" spans="2:16">
       <c r="C6" s="118" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -7500,7 +7508,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="121" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="2:16">
@@ -7508,7 +7516,7 @@
       <c r="E13" s="123"/>
       <c r="F13" s="124"/>
       <c r="G13" s="125" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H13" s="124"/>
       <c r="I13" s="126"/>
@@ -7516,7 +7524,7 @@
       <c r="K13" s="124"/>
       <c r="L13" s="124"/>
       <c r="M13" s="125" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N13" s="126"/>
       <c r="O13" s="122"/>
@@ -7530,34 +7538,34 @@
         <v>37</v>
       </c>
       <c r="E14" s="136" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F14" s="136" t="s">
+        <v>512</v>
+      </c>
+      <c r="G14" s="136" t="s">
         <v>514</v>
       </c>
-      <c r="G14" s="136" t="s">
-        <v>516</v>
-      </c>
       <c r="H14" s="136" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="I14" s="136" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J14" s="136" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K14" s="136" t="s">
+        <v>512</v>
+      </c>
+      <c r="L14" s="136" t="s">
         <v>514</v>
       </c>
-      <c r="L14" s="136" t="s">
-        <v>516</v>
-      </c>
       <c r="M14" s="136" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N14" s="136" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -7566,7 +7574,7 @@
         <v>(D15に関数入力)</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>12</v>
@@ -7666,23 +7674,23 @@
     </row>
     <row r="23" spans="3:14">
       <c r="C23" s="129" t="s">
+        <v>508</v>
+      </c>
+      <c r="D23" s="130" t="s">
+        <v>509</v>
+      </c>
+      <c r="E23" s="185" t="s">
         <v>510</v>
-      </c>
-      <c r="D23" s="130" t="s">
-        <v>511</v>
-      </c>
-      <c r="E23" s="185" t="s">
-        <v>512</v>
       </c>
       <c r="F23" s="186"/>
     </row>
     <row r="24" spans="3:14">
       <c r="C24" s="139"/>
       <c r="D24" s="132" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E24" s="187" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F24" s="187"/>
     </row>
@@ -7692,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="188" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F25" s="188"/>
     </row>
@@ -7702,7 +7710,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="189" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F26" s="189"/>
     </row>
@@ -7712,48 +7720,48 @@
         <v>2</v>
       </c>
       <c r="E27" s="188" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F27" s="188"/>
     </row>
     <row r="29" spans="3:14">
       <c r="D29" s="137" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E29" s="117" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="30" spans="3:14">
       <c r="D30" s="138"/>
       <c r="E30" s="117" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31" spans="3:14">
       <c r="E31" s="117" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="32" spans="3:14">
       <c r="E32" s="117" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="33" spans="4:5">
       <c r="D33" s="138" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E33" s="117" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="34" spans="4:5">
       <c r="D34" s="138" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E34" s="117" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="4:5">
@@ -7776,10 +7784,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9CBCEE-3B31-4688-94AB-19F8F6D98371}">
   <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="5" width="17.125" customWidth="1"/>
-    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="3" max="5" width="17.08203125" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7796,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="114" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D2" s="115"/>
       <c r="E2" s="115"/>
@@ -7808,7 +7816,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="114" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D3" s="115"/>
       <c r="E3" s="115"/>
@@ -7822,7 +7830,7 @@
     <row r="6" spans="1:6">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7935,7 +7943,7 @@
         <v>196</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -7949,16 +7957,16 @@
         <v>191</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -8031,7 +8039,7 @@
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -8050,19 +8058,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A2:H40"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
     <col min="5" max="6" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8093,7 +8101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="19.5" thickBot="1">
+    <row r="6" spans="2:6" ht="18.5" thickBot="1">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
         <v>203</v>
@@ -8159,7 +8167,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="19.5" thickBot="1">
+    <row r="12" spans="2:6" ht="18.5" thickBot="1">
       <c r="B12" s="6"/>
       <c r="E12" s="20" t="s">
         <v>174</v>
@@ -8419,19 +8427,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A2:H40"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
     <col min="5" max="6" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8462,7 +8470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="19.5" thickBot="1">
+    <row r="6" spans="2:6" ht="18.5" thickBot="1">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
         <v>205</v>
@@ -8510,7 +8518,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="19.5" thickBot="1">
+    <row r="10" spans="2:6" ht="18.5" thickBot="1">
       <c r="B10" s="6"/>
       <c r="E10" s="20" t="s">
         <v>172</v>
@@ -8716,12 +8724,12 @@
     </row>
     <row r="38" spans="2:4">
       <c r="B38" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="19.5" thickBot="1">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="18.5" thickBot="1">
       <c r="B39" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>38</v>
@@ -8730,9 +8738,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="19.5" thickBot="1">
+    <row r="40" spans="2:4" ht="18.5" thickBot="1">
       <c r="C40" s="112" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D40" s="113">
         <v>300</v>
@@ -8749,18 +8757,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A2:H20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
     <col min="5" max="6" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8894,20 +8902,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:H36"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="27.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9028,13 +9036,13 @@
         <v>181</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="H18" t="s">
         <v>545</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="H18" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -9053,22 +9061,22 @@
         <v>6</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="H20" s="144" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="H21" s="144" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="H22" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -9082,7 +9090,7 @@
         <v>264</v>
       </c>
       <c r="H23" s="145" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -9129,7 +9137,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -9138,7 +9146,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -9167,7 +9175,7 @@
         <v>9</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -9176,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -9223,50 +9231,50 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:CL49"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="16.08203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="26.875" customWidth="1"/>
-    <col min="6" max="6" width="10.375" customWidth="1"/>
-    <col min="7" max="7" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="14.25" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="36" max="53" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="53" width="7.58203125" bestFit="1" customWidth="1"/>
     <col min="54" max="56" width="14.25" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="59" max="61" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="63" max="80" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="80" width="7.58203125" bestFit="1" customWidth="1"/>
     <col min="81" max="81" width="13.75" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="31.375" bestFit="1" customWidth="1"/>
-    <col min="86" max="89" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="86" max="89" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="10.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -10701,7 +10709,7 @@
     </row>
     <row r="34" spans="1:89">
       <c r="D34" s="31" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>264</v>
@@ -10796,7 +10804,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -10896,7 +10904,7 @@
         <v>101</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" spans="1:89">
@@ -10904,7 +10912,7 @@
         <v>103</v>
       </c>
       <c r="E38" s="32" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="39" spans="1:89">
@@ -10912,7 +10920,7 @@
         <v>107</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="40" spans="1:89">
@@ -10920,7 +10928,7 @@
         <v>121</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="41" spans="1:89">
@@ -10928,7 +10936,7 @@
         <v>144</v>
       </c>
       <c r="E41" s="32" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="42" spans="1:89">
@@ -10936,7 +10944,7 @@
         <v>145</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="43" spans="1:89">
@@ -10944,7 +10952,7 @@
         <v>154</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44" spans="1:89">
@@ -10952,7 +10960,7 @@
         <v>155</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="45" spans="1:89">
@@ -10960,7 +10968,7 @@
         <v>171</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="46" spans="1:89">
@@ -10968,7 +10976,7 @@
         <v>901</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="47" spans="1:89">
@@ -10976,7 +10984,7 @@
         <v>907</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48" spans="1:89">
@@ -10984,7 +10992,7 @@
         <v>903</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="49" spans="4:5">
@@ -10992,7 +11000,7 @@
         <v>1001</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -11005,27 +11013,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:AC28"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.75" customWidth="1"/>
     <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.58203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.25" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12.25" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9.25" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9.25" customWidth="1"/>
-    <col min="25" max="26" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12.25" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.25" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="6.75" bestFit="1" customWidth="1"/>
@@ -11073,7 +11081,7 @@
         <v>164</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="2:8">
@@ -11099,10 +11107,10 @@
         <v>264</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H10" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -11119,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" spans="2:8">
@@ -11136,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -11148,7 +11156,7 @@
         <v>194</v>
       </c>
       <c r="H13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="2:8">
@@ -11205,7 +11213,7 @@
         <v>196</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -11258,7 +11266,7 @@
         <v>97</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="T22" s="8" t="s">
         <v>98</v>
@@ -11273,7 +11281,7 @@
         <v>101</v>
       </c>
       <c r="X22" s="8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Y22" s="8" t="s">
         <v>102</v>
@@ -11444,39 +11452,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A2:AL319"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="13.625" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="29.625" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="29.58203125" customWidth="1"/>
     <col min="5" max="5" width="29.25" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="8" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="34.08203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.375" customWidth="1"/>
-    <col min="24" max="24" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.33203125" customWidth="1"/>
+    <col min="24" max="24" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.58203125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
@@ -11592,89 +11600,89 @@
       <c r="C11" s="65" t="s">
         <v>301</v>
       </c>
-      <c r="D11" s="156" t="s">
+      <c r="D11" s="151" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="157"/>
-      <c r="F11" s="156" t="s">
+      <c r="E11" s="152"/>
+      <c r="F11" s="151" t="s">
         <v>296</v>
       </c>
-      <c r="G11" s="157"/>
+      <c r="G11" s="152"/>
       <c r="L11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="2:12">
-      <c r="B12" s="172" t="s">
+      <c r="B12" s="150" t="s">
         <v>275</v>
       </c>
       <c r="C12" s="42">
         <v>0</v>
       </c>
-      <c r="D12" s="168" t="s">
+      <c r="D12" s="153" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="169"/>
-      <c r="F12" s="158" t="s">
+      <c r="E12" s="154"/>
+      <c r="F12" s="167" t="s">
         <v>297</v>
       </c>
-      <c r="G12" s="159"/>
+      <c r="G12" s="168"/>
       <c r="L12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="172"/>
+      <c r="B13" s="150"/>
       <c r="C13" s="42">
         <v>1</v>
       </c>
-      <c r="D13" s="168" t="s">
+      <c r="D13" s="153" t="s">
         <v>200</v>
       </c>
-      <c r="E13" s="169"/>
-      <c r="F13" s="160" t="s">
+      <c r="E13" s="154"/>
+      <c r="F13" s="169" t="s">
         <v>304</v>
       </c>
-      <c r="G13" s="161"/>
+      <c r="G13" s="170"/>
       <c r="L13" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="2:12">
-      <c r="B14" s="172"/>
+      <c r="B14" s="150"/>
       <c r="C14" s="42">
         <v>2</v>
       </c>
-      <c r="D14" s="168" t="s">
+      <c r="D14" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="E14" s="169"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="161"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="169"/>
+      <c r="G14" s="170"/>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="172"/>
+      <c r="B15" s="150"/>
       <c r="C15" s="42">
         <v>3</v>
       </c>
-      <c r="D15" s="168" t="s">
+      <c r="D15" s="153" t="s">
         <v>262</v>
       </c>
-      <c r="E15" s="169"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="161"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="170"/>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="172"/>
+      <c r="B16" s="150"/>
       <c r="C16" s="42">
         <v>4</v>
       </c>
-      <c r="D16" s="168" t="s">
+      <c r="D16" s="153" t="s">
         <v>263</v>
       </c>
-      <c r="E16" s="169"/>
-      <c r="F16" s="162"/>
-      <c r="G16" s="163"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="163"/>
+      <c r="G16" s="164"/>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="58" t="s">
@@ -11729,30 +11737,30 @@
       <c r="G20" s="62"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="170" t="s">
+      <c r="B21" s="148" t="s">
         <v>284</v>
       </c>
       <c r="C21" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="168" t="s">
+      <c r="D21" s="153" t="s">
         <v>302</v>
       </c>
-      <c r="E21" s="169"/>
+      <c r="E21" s="154"/>
       <c r="F21" s="66" t="s">
         <v>297</v>
       </c>
       <c r="G21" s="67"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="170"/>
+      <c r="B22" s="148"/>
       <c r="C22" s="42" t="b">
         <v>0</v>
       </c>
-      <c r="D22" s="168" t="s">
+      <c r="D22" s="153" t="s">
         <v>303</v>
       </c>
-      <c r="E22" s="169"/>
+      <c r="E22" s="154"/>
       <c r="F22" s="68" t="s">
         <v>305</v>
       </c>
@@ -11775,130 +11783,130 @@
       <c r="G23" s="64"/>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="170" t="s">
+      <c r="B24" s="148" t="s">
         <v>287</v>
       </c>
       <c r="C24" s="41">
         <v>1</v>
       </c>
-      <c r="D24" s="166" t="s">
+      <c r="D24" s="155" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="167"/>
-      <c r="F24" s="164" t="s">
+      <c r="E24" s="156"/>
+      <c r="F24" s="161" t="s">
         <v>297</v>
       </c>
-      <c r="G24" s="165"/>
+      <c r="G24" s="162"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="170"/>
+      <c r="B25" s="148"/>
       <c r="C25" s="41">
         <v>2</v>
       </c>
-      <c r="D25" s="154" t="s">
+      <c r="D25" s="157" t="s">
         <v>276</v>
       </c>
-      <c r="E25" s="155"/>
-      <c r="F25" s="148" t="s">
+      <c r="E25" s="158"/>
+      <c r="F25" s="165" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="149"/>
+      <c r="G25" s="166"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="170"/>
+      <c r="B26" s="148"/>
       <c r="C26" s="41">
         <v>3</v>
       </c>
-      <c r="D26" s="154" t="s">
+      <c r="D26" s="157" t="s">
         <v>277</v>
       </c>
-      <c r="E26" s="155"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="149"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="166"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="170"/>
+      <c r="B27" s="148"/>
       <c r="C27" s="41">
         <v>4</v>
       </c>
-      <c r="D27" s="154" t="s">
+      <c r="D27" s="157" t="s">
         <v>278</v>
       </c>
-      <c r="E27" s="155"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="149"/>
+      <c r="E27" s="158"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="166"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="170"/>
+      <c r="B28" s="148"/>
       <c r="C28" s="41">
         <v>5</v>
       </c>
-      <c r="D28" s="154" t="s">
+      <c r="D28" s="157" t="s">
         <v>279</v>
       </c>
-      <c r="E28" s="155"/>
-      <c r="F28" s="152"/>
-      <c r="G28" s="153"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="159"/>
+      <c r="G28" s="160"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="170" t="s">
+      <c r="B29" s="148" t="s">
         <v>288</v>
       </c>
       <c r="C29" s="41">
         <v>1</v>
       </c>
-      <c r="D29" s="166" t="s">
+      <c r="D29" s="155" t="s">
         <v>286</v>
       </c>
-      <c r="E29" s="167"/>
-      <c r="F29" s="164" t="s">
+      <c r="E29" s="156"/>
+      <c r="F29" s="161" t="s">
         <v>297</v>
       </c>
-      <c r="G29" s="165"/>
+      <c r="G29" s="162"/>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="170"/>
+      <c r="B30" s="148"/>
       <c r="C30" s="41">
         <v>2</v>
       </c>
-      <c r="D30" s="154" t="s">
+      <c r="D30" s="157" t="s">
         <v>280</v>
       </c>
-      <c r="E30" s="155"/>
-      <c r="F30" s="148" t="s">
+      <c r="E30" s="158"/>
+      <c r="F30" s="165" t="s">
         <v>304</v>
       </c>
-      <c r="G30" s="149"/>
+      <c r="G30" s="166"/>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="171" t="s">
+      <c r="B31" s="149" t="s">
         <v>289</v>
       </c>
       <c r="C31" s="41">
         <v>2</v>
       </c>
-      <c r="D31" s="154" t="s">
+      <c r="D31" s="157" t="s">
         <v>281</v>
       </c>
-      <c r="E31" s="155"/>
-      <c r="F31" s="150" t="s">
+      <c r="E31" s="158"/>
+      <c r="F31" s="171" t="s">
         <v>297</v>
       </c>
-      <c r="G31" s="151"/>
+      <c r="G31" s="172"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="171"/>
+      <c r="B32" s="149"/>
       <c r="C32" s="41">
         <v>3</v>
       </c>
-      <c r="D32" s="154" t="s">
+      <c r="D32" s="157" t="s">
         <v>282</v>
       </c>
-      <c r="E32" s="155"/>
-      <c r="F32" s="152" t="s">
+      <c r="E32" s="158"/>
+      <c r="F32" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="G32" s="153"/>
+      <c r="G32" s="160"/>
     </row>
     <row r="33" spans="1:37">
       <c r="B33" s="6"/>
@@ -12003,7 +12011,7 @@
         <v>127</v>
       </c>
       <c r="W39" s="8" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X39" s="8" t="s">
         <v>128</v>
@@ -12112,7 +12120,7 @@
         <v>83</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="X40" s="7" t="s">
         <v>83</v>
@@ -12412,7 +12420,7 @@
         <v>83</v>
       </c>
       <c r="W44" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="X44" s="7" t="s">
         <v>83</v>
@@ -22761,43 +22769,43 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
@@ -22825,28 +22833,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:Y28"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="11.75" customWidth="1"/>
-    <col min="3" max="3" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.58203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.25" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.08203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.08203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="9" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -22896,7 +22904,7 @@
         <v>288</v>
       </c>
       <c r="F7" s="90" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -22925,13 +22933,13 @@
         <v>288</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J10" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="2:10">
@@ -22945,13 +22953,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I11" s="23" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" spans="2:10">
@@ -22971,7 +22979,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="2:10">
@@ -22982,7 +22990,7 @@
         <v>199</v>
       </c>
       <c r="J13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="14" spans="2:10">
@@ -23015,7 +23023,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -23357,11 +23365,11 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:F28"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="3" width="26.625" customWidth="1"/>
-    <col min="4" max="4" width="28.875" customWidth="1"/>
+    <col min="2" max="2" width="17.58203125" customWidth="1"/>
+    <col min="3" max="3" width="26.58203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="23.75" customWidth="1"/>
     <col min="6" max="6" width="33.25" customWidth="1"/>
   </cols>
@@ -23510,10 +23518,10 @@
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="2:3">
@@ -23558,10 +23566,10 @@
     </row>
     <row r="28" spans="2:3">
       <c r="B28" s="23" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -23577,13 +23585,13 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:H23"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
     <col min="3" max="3" width="29.75" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
-    <col min="5" max="5" width="35.875" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
@@ -23591,7 +23599,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D2" s="4"/>
     </row>
@@ -23621,7 +23629,7 @@
     <row r="7" spans="1:8">
       <c r="B7" s="6"/>
       <c r="C7" s="8" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>221</v>
@@ -23639,7 +23647,7 @@
     <row r="8" spans="1:8">
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>223</v>
@@ -23668,7 +23676,7 @@
         <v>196</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -23702,7 +23710,7 @@
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="31" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>264</v>
@@ -23710,18 +23718,18 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="23" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="23" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -23761,13 +23769,13 @@
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A2:H19"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="19.875" customWidth="1"/>
-    <col min="3" max="3" width="26.875" customWidth="1"/>
-    <col min="4" max="4" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
     <col min="5" max="5" width="47.75" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="6" max="6" width="16.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8">
@@ -23775,7 +23783,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D2" s="4"/>
     </row>
@@ -23784,7 +23792,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D3" s="4"/>
     </row>
@@ -23796,7 +23804,7 @@
     <row r="6" spans="1:8">
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H6" t="s">
         <v>184</v>
@@ -23808,7 +23816,7 @@
         <v>221</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>246</v>
@@ -23852,7 +23860,7 @@
         <v>196</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -23873,10 +23881,10 @@
         <v>(D14に関数入力)</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15" spans="1:8">
